--- a/AAII_Financials/Quarterly/KKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>KKR</t>
   </si>
@@ -656,383 +656,389 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6653600</v>
+      </c>
+      <c r="E8" s="3">
         <v>4203600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7871000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7105000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6174900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4500200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4465600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6279300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5063600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10613300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5860100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5074000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4516800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3212700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3013100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2020600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>405700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1223800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4195800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4648100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3258500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4598400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2118800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1984700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1392900</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="3">
         <v>1151200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>848000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1271700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1291000</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI8" s="3">
         <v>1203600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>971600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>472600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1024100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>749700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1015800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>767800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>481500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>687100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3652400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2325000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3199400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3162300</v>
       </c>
-      <c r="G9" s="3">
-        <v>2872500</v>
-      </c>
       <c r="H9" s="3">
+        <v>3239400</v>
+      </c>
+      <c r="I9" s="3">
         <v>2093500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1507100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2471100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2232000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7257300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2377200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>764900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1736200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1571300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1664100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1156800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-66600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>841400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1729300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1956800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>625800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1563000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>113700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>89500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>60900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>35400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>88100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>57500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>91900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>103500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>94100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>73900</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1054,107 +1060,110 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3001200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1878600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4671600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3942700</v>
       </c>
-      <c r="G10" s="3">
-        <v>3302400</v>
-      </c>
       <c r="H10" s="3">
+        <v>2935500</v>
+      </c>
+      <c r="I10" s="3">
         <v>2406800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2958500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3808200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2831600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3356000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3482900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4309100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2780600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1641400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1349000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>863800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>472300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>382400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2466500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2691300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2632700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3035400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2005100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1895200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>1063100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>790500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1179800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1187500</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3">
         <v>1129700</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1176,8 +1185,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1220,8 +1232,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1342,8 +1355,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1464,8 +1480,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1508,23 +1527,23 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>6400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1586,88 +1605,91 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E15" s="3">
         <v>36200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>23300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>23200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>22300</v>
       </c>
       <c r="L15" s="3">
         <v>22300</v>
       </c>
       <c r="M15" s="3">
+        <v>22300</v>
+      </c>
+      <c r="N15" s="3">
         <v>22100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>21000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>14800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>14200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>12900</v>
-      </c>
-      <c r="V15" s="3">
-        <v>11300</v>
       </c>
       <c r="W15" s="3">
         <v>11300</v>
       </c>
       <c r="X15" s="3">
+        <v>11300</v>
+      </c>
+      <c r="Y15" s="3">
         <v>11000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4600</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>4800</v>
       </c>
       <c r="AB15" s="3">
         <v>4800</v>
       </c>
       <c r="AC15" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="AD15" s="3">
         <v>4700</v>
@@ -1676,40 +1698,43 @@
         <v>4700</v>
       </c>
       <c r="AF15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AG15" s="3">
         <v>4900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>3700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>3600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>3700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>3900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>4200</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>4000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1749,252 +1774,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5279600</v>
+      </c>
+      <c r="E17" s="3">
         <v>3740700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5271200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4905400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4646100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3729200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2823000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4634700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3853400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9250300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3984100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2254800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3065800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2804300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2889300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1838400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>647000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1582200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3291200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3350000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2114000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3131900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1292700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1183200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>817900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>-61300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>839400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>677000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>900700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>832200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>331900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>814000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>675100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>436600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>636700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>530200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>629700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>540000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>452800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>511100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="E18" s="3">
         <v>462900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2599800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2199600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1528800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>771100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1642600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1644600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1210200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1363100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1876000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2819200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1451000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>408400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>123800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>182200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-241300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-358400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>904600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1298100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1144500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1466500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>826100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>801500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>575000</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>311800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>171000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>371000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>458800</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>389600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>296600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>36000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>387400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>219500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>386100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>227800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>28700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2037,8 +2069,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2081,208 +2114,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>554200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>415500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1346600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1929200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>397700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2641000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3727100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3139400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4242800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2755900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1822500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1405900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>487500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1420900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1585000</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>1044300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1534700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>804100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>485600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>389900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>699600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>797500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>622300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>1064700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1401100</v>
+      </c>
+      <c r="E21" s="3">
         <v>499100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2625600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2226400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1553100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>794400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1665500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1667800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1232500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1385400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1898100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2841900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1472000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>428600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>678500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>599000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1587700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1583500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1303900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3939100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4871900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4616900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5068600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3557200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2397500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>1717700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>658500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1791700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2048600</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>1433800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1831300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>843800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>872900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>609200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1085300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1029500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>677200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1240800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2325,330 +2364,339 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>548800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>391500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>328700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>281800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>275400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>278200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>265100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>251800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>244600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>223700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>240100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>261500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>261000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>268700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>264800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>249100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>241500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>211100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>203900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>219600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>211500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>212000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>198600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>186900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>182100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>255100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="E23" s="3">
         <v>462900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2599800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2199600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1528800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>771100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1642600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1644600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1210200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1363100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1876000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2819200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1451000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>408400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>129100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>206200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1916600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1289000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1026900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3660900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4606500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4354100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4824200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3333700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2157400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4588600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1456800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>389700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1527100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1794600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1213900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1222900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1627400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>620500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>661500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>397400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>887100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>838400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>468800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>985600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>246100</v>
+      </c>
+      <c r="E24" s="3">
         <v>185400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>333100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>359700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>174300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>86600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>258300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>209900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>217000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>269200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>286600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>437200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>325000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>148700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>109600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>81700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-102500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>36700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>191600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>379300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>343700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>438700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>404100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>359400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>206300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-360700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>142600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>53100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>165400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>167600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-143300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-129400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>61000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>17600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>48900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>18400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>18500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>40500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>5800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2769,252 +2817,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1127900</v>
+      </c>
+      <c r="E26" s="3">
         <v>277500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2266600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1839800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1354500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>684500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1384300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1434700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>993200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1093900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1589400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2382000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1126100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>259700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>124500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1814100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1252400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>835300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3281600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4262900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3915400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4420100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2974300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1951200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4228000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1314200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>336600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1361700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1627000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1070600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1352300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1566400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>602900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>612600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>378900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>868500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>797900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>463000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>974800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>660100</v>
+      </c>
+      <c r="E27" s="3">
         <v>364800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1092000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>859900</v>
       </c>
-      <c r="G27" s="3">
-        <v>485900</v>
-      </c>
       <c r="H27" s="3">
+        <v>472400</v>
+      </c>
+      <c r="I27" s="3">
         <v>-199400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1125600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>600600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>667900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>682200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1040400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1472900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>844500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>322700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>121100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>32600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-734600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>507600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1131400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1277700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1644200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1479700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1056500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>698600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1288900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>515100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>241200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>514400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>701000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-393000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>640200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>680400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>170100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>264300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>153600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>405600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>259300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>171000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>352200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3135,8 +3192,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3221,8 +3281,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3239,12 +3299,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-97900</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3257,8 +3317,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3379,8 +3442,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3501,8 +3567,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3545,208 +3614,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-554200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-415500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1346600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1929200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-397700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2641000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3727100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3139400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4242800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2755900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1822500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1405900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-487500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1420900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1585000</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-1044300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1534700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-804100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-485600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-389900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-699600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-797500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-622300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-1064700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700500</v>
+      </c>
+      <c r="E33" s="3">
         <v>405200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1145900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>900400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>510100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-185900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1125600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>600600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>667900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>682200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1040400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1490100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>861700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>340000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>121100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>32600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-734600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>507600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1131400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1277700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1644200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1479700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1056500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>698600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1288900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>515100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>241200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>514400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>701000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-393000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>640200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>680400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>170100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>166400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>153600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>405600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>259300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>171000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>352200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3867,257 +3942,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700500</v>
+      </c>
+      <c r="E35" s="3">
         <v>405200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1145900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>900400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>510100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-185900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1125600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>600600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>667900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>682200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1040400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1490100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>861700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>340000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>121100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>32600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-734600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>507600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1131400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1277700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1644200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1479700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1056500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>698600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1288900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>515100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>241200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>514400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>701000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-393000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>640200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>680400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>170100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>166400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>153600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>405600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>259300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>171000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>352200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4160,8 +4244,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4204,175 +4289,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21080100</v>
+      </c>
+      <c r="E41" s="3">
         <v>19200100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16892100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22681900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17824200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17986900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14878500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14459800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15540200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15608900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20348600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11294400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10306500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9289500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12823600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11058800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11851200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12914900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10091600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11973600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11662300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10498700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6507900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5744100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3605100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3153500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3163200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3542400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3098800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2719800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2445100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3228700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3204700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2748900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3679100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3766300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3608700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4358300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4133700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3473100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26476500</v>
+      </c>
+      <c r="E42" s="3">
         <v>26099500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25729800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>23429600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22372200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22356900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22000500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24421500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25166400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>28312100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>19120600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13454400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14154700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14252400</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4448,130 +4537,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5932200</v>
+      </c>
+      <c r="E43" s="3">
         <v>6769000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6072400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>51811600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50889100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>50246800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4643500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>51454700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>49883400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4326500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3638600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3991900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3876800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4186600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>410300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>331300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>198900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>259000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>590400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>522600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>521900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>392200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>865300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>503100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>555700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>289100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>248100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>455100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>563900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>781400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>665300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>708200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>676400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>629800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1010300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1207600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1032400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>769500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1292400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1041400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4614,8 +4709,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4692,175 +4787,181 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2468600</v>
+      </c>
+      <c r="E45" s="3">
         <v>2440200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2673400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2749500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3043000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2902100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3036400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2774700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2944400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2835300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3024700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2995400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3133100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2912600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>59800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>50500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>37100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>33700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>24500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>26400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>29300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>18700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>17800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>14600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>28700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>25900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>27100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>23600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>29300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>21300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>23500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>25700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>30200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>15200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>18000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>17800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56079500</v>
+      </c>
+      <c r="E46" s="3">
         <v>54794100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>51627400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>100877200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>94360500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>93899200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>45048400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>93613300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>94063900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>51639400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>46592000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32152500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31913400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31080100</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4936,320 +5037,329 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>258443900</v>
+      </c>
+      <c r="E47" s="3">
         <v>258371100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>262077500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>251239700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>240995900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>233851100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>224029800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>236757200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>224830100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>215809500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>197143700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>196377600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>195023300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>191966700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>218237900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>209863800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>209251200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>212847900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>213763500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>212226000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>185534800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>175488700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>70147700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>61759000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>55355300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>49453600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>55653700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>51503100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>51919000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>46529400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45565200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>44801600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>43237100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>42667600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>39568300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>37735800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>36662500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>34548700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>31660200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>31621100</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1905600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1833100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1839500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1845500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1802000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1758300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1769400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1727800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1356400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1369100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1394700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1399100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1420900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1386600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1377000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1250600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1259700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1210900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1209400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1200800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1189100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1135400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>951400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>882900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>792800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>781100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>754100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>732400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>726200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>612400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>451200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>422400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>401400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>369000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>364200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>341800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>323000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>300600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>283300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6793600</v>
+      </c>
+      <c r="E49" s="3">
         <v>6368400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8782000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8727100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8477900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6336300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8020000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8072800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7616200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7657400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7393800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5338000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5341400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5478300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4673700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3762100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3814800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1564800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1490600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1362600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1277600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1173300</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>83500</v>
       </c>
       <c r="Z49" s="3">
         <v>83500</v>
@@ -5264,46 +5374,49 @@
         <v>83500</v>
       </c>
       <c r="AD49" s="3">
+        <v>83500</v>
+      </c>
+      <c r="AE49" s="3">
         <v>91600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>92400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>92600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>93400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>94200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>94900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>208000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>212700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>100900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>102800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>218000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>224000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>231500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5424,8 +5537,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5546,130 +5662,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>85553000</v>
+      </c>
+      <c r="E52" s="3">
         <v>85042900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>82917600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>33111300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>32417500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31873700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>78372900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17834600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17788300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>60799100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62428500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50774300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>51796400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50550500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>633000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>640600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>638300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>739000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>538400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>649400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>466400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>584500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>592200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>339300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>578700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>713100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>245200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>348500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>392400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>488600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>748400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>371000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>203200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>250100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>390800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>432600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>441900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>527300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>502500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5790,130 +5912,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>414463200</v>
+      </c>
+      <c r="E54" s="3">
         <v>412084500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>410144100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>398480900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>380867600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>372372900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>360099400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>360655900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>348469200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>339773900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>317294200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>288733000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>287694800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>282610600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>275346600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>266248600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>266075100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>266291000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>264285400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>265799700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>229234900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>216445100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>79806500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70655300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>62110400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>55601100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60899300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57645000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57524100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>52004000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>50743400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>50343900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>48572700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>47579200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>45834700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>44305600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>42868100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>41635700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>39002900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>37984600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5956,8 +6084,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6000,205 +6129,209 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4906000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4716100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3410900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4168100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3190700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3310800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2886200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2387600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2241300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2189700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1034600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1217400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>906400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1296400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2089300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2234500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2684800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3308900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3837900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3724600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3355700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2939100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2047300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1550300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1094300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>882000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1567300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1454500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1415500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1197200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1053500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1426400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1356500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1287600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1373500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1262600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1280400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1154300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1106900</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1204400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1928400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1860400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3033200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1998700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2324000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>975400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>781900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1008600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1127600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1330500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1948600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1843500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1879100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1214600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>158800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>87900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>85800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>136100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>249400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>262200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>292100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>243500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>281800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>434600</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
@@ -6244,175 +6377,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>49967800</v>
+      </c>
+      <c r="E59" s="3">
         <v>49527800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>47029000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45588400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44323300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44505000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44071100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45663300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44133700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42906800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>34527900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23625500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24342100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24019800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28919600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27946400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>29313800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27783600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27833900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>29620500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>19581900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>19011600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>937700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1232200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>922000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>812900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>809800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>978800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>844900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>620900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>910700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>683500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>579300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>564400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>832700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>748000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>669500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>590900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>671400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65475600</v>
+      </c>
+      <c r="E60" s="3">
         <v>63951800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60961200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>59221200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>56934500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55269100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53381000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55469900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53048000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51437300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41948600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31297500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31260300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30223900</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6488,228 +6627,234 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54235500</v>
+      </c>
+      <c r="E61" s="3">
         <v>53919700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>52975400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54063700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52119400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>50485200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50555000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>50312300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>49587700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48677600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48029100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>46553800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>46628100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45230900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>42726800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>40178700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>39152900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>38142600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>38577800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>41151100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37752400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>36069800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33423600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>31451600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28676900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>26265400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>27013300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25281200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>25685800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22262400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>22341200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20266200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>19972400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>22041300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>21193900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>20290700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>19425300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>19625400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>18544100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>17589400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>211394300</v>
+      </c>
+      <c r="E62" s="3">
         <v>210347600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>211514900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>206840200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>197863500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>194694900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>191338400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>190367100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>184735200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>180334500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>166567400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>147174100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>147318800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>148338800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1723800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1980600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>233700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>846600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>978700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1167700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>971500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>729100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>276100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>68700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>67500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>66400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>65700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>67700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>67600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>67400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>66800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>59800</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>58400</v>
       </c>
       <c r="AJ62" s="3">
         <v>58400</v>
@@ -6717,8 +6862,8 @@
       <c r="AK62" s="3">
         <v>58400</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>5</v>
+      <c r="AL62" s="3">
+        <v>58400</v>
       </c>
       <c r="AM62" s="3" t="s">
         <v>5</v>
@@ -6732,8 +6877,11 @@
       <c r="AP62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6854,8 +7002,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6976,8 +7127,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7098,130 +7252,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>334013000</v>
+      </c>
+      <c r="E66" s="3">
         <v>331278300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>328512200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>323079000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>309899100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>303416000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>298114700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>298857300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>289939200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>282862100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>258915300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>227134800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>227100400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>225487200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>256538900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>248797600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>247002400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>250576700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>246703300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>248866700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>213166500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>201769100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66089700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>58457700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>52155500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46275100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>50091800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>47527300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>47648600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>42681600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>42093800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>41337200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>40180300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>40178400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>38648800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>37442400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>36173000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>35397800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>33063100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>32168000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7264,8 +7424,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7386,8 +7547,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7508,8 +7672,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7529,7 +7696,7 @@
         <v>2543400</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>2543400</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -7547,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>1115800</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>1115800</v>
@@ -7562,28 +7729,28 @@
         <v>1115800</v>
       </c>
       <c r="T70" s="3">
-        <v>1118400</v>
+        <v>1115800</v>
       </c>
       <c r="U70" s="3">
         <v>1118400</v>
       </c>
       <c r="V70" s="3">
+        <v>1118400</v>
+      </c>
+      <c r="W70" s="3">
         <v>1118500</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1268100</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1601100</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>1598300</v>
       </c>
       <c r="Z70" s="3">
         <v>1598300</v>
       </c>
       <c r="AA70" s="3">
-        <v>482600</v>
+        <v>1598300</v>
       </c>
       <c r="AB70" s="3">
         <v>482600</v>
@@ -7630,8 +7797,11 @@
       <c r="AP70" s="3">
         <v>482600</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>482600</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7752,107 +7922,110 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14569400</v>
+      </c>
+      <c r="E72" s="3">
         <v>14084400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13884400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12943800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12248700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11941100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12282500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11312400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10867200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10354500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9818300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8923900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7592600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6890400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6701100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6366000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6590900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7510700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7670200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7247400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6200600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5007200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3440800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2037900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1056900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>433500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1792200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1345800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1172800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>726300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>92000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>551000</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
@@ -7865,8 +8038,8 @@
       <c r="AM72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN72" s="3">
-        <v>0</v>
+      <c r="AN72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO72" s="3">
         <v>0</v>
@@ -7874,8 +8047,11 @@
       <c r="AP72" s="3">
         <v>0</v>
       </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7996,8 +8172,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8118,8 +8297,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8240,130 +8422,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28504000</v>
+      </c>
+      <c r="E76" s="3">
         <v>27952700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28359200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>27205800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25675800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24926600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23651600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24083700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21673100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21421200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22858700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20407800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18865800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18546900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17692000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16335300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17956900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14595900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16463800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15814500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14800300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13075000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12118500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10599300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9472300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8843400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10324900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9635200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9392900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8839800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8167100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8524200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7909800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6918200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6703400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6380700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6212600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5755400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5457300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5334000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8484,257 +8672,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700500</v>
+      </c>
+      <c r="E81" s="3">
         <v>405200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1145900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>900400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>510100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-185900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1125600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>600600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>667900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>682200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1040400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1490100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>861700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>340000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>121100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>32600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-734600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>507600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1131400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1277700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1644200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1479700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1056500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>698600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1288900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>515100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>241200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>514400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>701000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-393000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>640200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>680400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>170100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>166400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>153600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>405600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>259300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>171000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>352200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8777,53 +8974,54 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E83" s="3">
         <v>18600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>17900</v>
       </c>
       <c r="H83" s="3">
         <v>17900</v>
       </c>
       <c r="I83" s="3">
+        <v>17900</v>
+      </c>
+      <c r="J83" s="3">
         <v>17700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12700</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -8899,8 +9097,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9021,8 +9222,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9143,8 +9347,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9265,8 +9472,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9387,8 +9597,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9509,130 +9722,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3252500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1746700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4900300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2389600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>438800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2549700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-111700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1876300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3357800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1527400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1107100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1971100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2639100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1932900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-647500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1485100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4063500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>916800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3618200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2251200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1234100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-73200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1806300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1409400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1331500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1406400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2169400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-398900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3270100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>156300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2366400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-701700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2380800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2157500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1313500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-355200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-745100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-1118400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-1006400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>635100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9675,130 +9894,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-67400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-53200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-29200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-38600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-24400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-33000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-41900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-32300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-41400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-32700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-36500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-26200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-26900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-42800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-54500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9919,8 +10142,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10041,130 +10267,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>634900</v>
+      </c>
+      <c r="E94" s="3">
         <v>2347900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4238500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7005900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1890100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3147300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2252700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5119300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5476600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6198800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>813000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1076800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>199400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3818500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2966100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3589100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5094200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1997800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4468700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2172500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-376000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-41900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-30200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-45400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-43500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-18700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-125200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-35300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>36700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>61800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-85700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-52200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10207,130 +10439,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>175100</v>
+      </c>
+      <c r="E96" s="3">
         <v>164800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>164900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>164800</v>
       </c>
       <c r="G96" s="3">
         <v>164800</v>
       </c>
       <c r="H96" s="3">
-        <v>155400</v>
+        <v>164800</v>
       </c>
       <c r="I96" s="3">
         <v>155400</v>
       </c>
       <c r="J96" s="3">
-        <v>155300</v>
+        <v>155400</v>
       </c>
       <c r="K96" s="3">
         <v>155300</v>
       </c>
       <c r="L96" s="3">
-        <v>146000</v>
+        <v>155300</v>
       </c>
       <c r="M96" s="3">
         <v>146000</v>
       </c>
       <c r="N96" s="3">
+        <v>146000</v>
+      </c>
+      <c r="O96" s="3">
         <v>141500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>142300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>133500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-133500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-133300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-91900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-85700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-84800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-84500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-84300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-77800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-76800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-75500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-75300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-69700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-68800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-68100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-66600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-66100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-89200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-84300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-81200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-79900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-78500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-72400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-71900</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-71200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10451,8 +10687,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10573,8 +10812,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10695,370 +10937,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2186400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1692600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3410800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9427600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>990800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3603100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2893700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2076500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2061100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>45000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7142700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>104100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3454300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2073000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5404300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4346000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8158500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4146500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4237900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7231400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4435600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4459100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2916300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3566200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1810900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1510200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1804900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>874400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3798400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>7200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1746500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>754400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2896900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1218200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>889800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>623400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>120700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1306100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1404200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E101" s="3">
         <v>20000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-123800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>59200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-38100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>34500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-36300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>21600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-35200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-171000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-49400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-35200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-14200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-171000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-49400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-17900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-17000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>11700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>37400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>28300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>19400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-25700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>19800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-21800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-14900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-32800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>20900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>9200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>19600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>43200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>7700</v>
       </c>
-      <c r="AO101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP101" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ101" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1716700</v>
+      </c>
+      <c r="E102" s="3">
         <v>2333700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5734700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4830300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-337300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3025500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>405500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1107300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-95800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4642600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9097300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>962100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1020200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3656900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1755500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-742400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1170100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3016100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1986500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>494500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1040700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3984200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1105500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2149300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>468600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>32600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-388200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>435000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>403800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>145300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-653100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>13000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>473400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-927100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-538100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>304900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-626700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>249500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>312100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>684300</v>
       </c>
     </row>
